--- a/public/training/library/training-samples/SBD-Training-POAM.xlsx
+++ b/public/training/library/training-samples/SBD-Training-POAM.xlsx
@@ -51,7 +51,7 @@
     <t xml:space="preserve">Columns</t>
   </si>
   <si>
-    <t xml:space="preserve">Field names follow CDSE's public POA&amp;M Job Aid (eMASS-style). One row per milestone: repeat the POA&amp;M ID on each milestone row of the same weakness.</t>
+    <t xml:space="preserve">Field names follow CDSE's public POA&amp;M Job Aid. One row per milestone: repeat the POA&amp;M ID on each milestone row of the same weakness.</t>
   </si>
   <si>
     <t xml:space="preserve">Risk</t>
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Notice</t>
   </si>
   <si>
-    <t xml:space="preserve">Written by Secure By Design for training. Not the eMASS POA&amp;M or an official form.</t>
+    <t xml:space="preserve">Written by Secure By Design for training. Not an official form.</t>
   </si>
   <si>
     <t xml:space="preserve">Plan of Action and Milestones (POA&amp;M)</t>

--- a/public/training/library/training-samples/SBD-Training-POAM.xlsx
+++ b/public/training/library/training-samples/SBD-Training-POAM.xlsx
@@ -30,7 +30,7 @@
     <t xml:space="preserve">SECURE BY DESIGN TRAINING SAMPLE - NOT AN OFFICIAL FORM. For instruction and practice with fictional data only.</t>
   </si>
   <si>
-    <t xml:space="preserve">[CLASSIFICATION: when filled in, mark this document as your security classification guide and PSO direct]</t>
+    <t/>
   </si>
   <si>
     <t xml:space="preserve">Plan of Action and Milestones (POA&amp;M) - training sample</t>
@@ -799,10 +799,8 @@
       </c>
       <c r="B1" s="1"/>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
-        <v>1</v>
-      </c>
+    <row r="2" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="4" customHeight="1">
+      <c r="A2" s="2"/>
       <c r="B2" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -960,10 +958,8 @@
       <c r="Y1" s="1"/>
       <c r="Z1" s="1"/>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
-        <v>1</v>
-      </c>
+    <row r="2" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="4" customHeight="1">
+      <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
@@ -6845,10 +6841,8 @@
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
-        <v>1</v>
-      </c>
+    <row r="2" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="4" customHeight="1">
+      <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
     </row>
